--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
   </si>
   <si>
     <t>Der Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine List-Ressource abgebildet. 
-Diese enthält 0..* Einträge (List.entry), wobei jedes Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
+Diese enthält 0..* Einträge (List.entry), wobei jeder Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
 Die Reihenfolge der Einträge kann durch den GDA festgelegt werden. Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
   </si>
   <si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Der Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine List-Ressource abgebildet. 
-Diese enthält 0..* Einträge (List.entry), wobei jeder Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
-Die Reihenfolge der Einträge kann durch den GDA festgelegt werden. Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
+    <t>Der Medikationsplan wird durch eine List-Ressource abgebildet. 
+Diese enthält 0..* Einträge (List.entry), wobei jedes List.entry.item genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) beinhaltet.
+Die Reihung der List.entries bestimmt die Reihenfolge der Medikationsplaneinträge. 
+Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -119,7 +120,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-list</t>
+    <t>http://hl7.org/fhir/StructureDefinition/List</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -469,7 +470,7 @@
 </t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste zur Integritätsprüfung beim Schreibvorgang.</t>
+    <t>Logischer Identfier der Liste (des Medikationsplans).</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -484,7 +485,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status der Liste. Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
+    <t>Status des Medikationsplans. Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -496,7 +497,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListStatusVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListStatusVS</t>
   </si>
   <si>
     <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
@@ -508,7 +509,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
+    <t>Der Medikationsplan ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -542,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t>Die Liste hat keinen Titel.</t>
+    <t>Der Medikationsplan hat keinen Titel.</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -607,8 +608,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den die Liste geführt wird, der über den 
-Zentralen Patientenindex identifizierbar und Teilnehmer der ELGA-Anwendung ist.</t>
+    <t>ELGA-Teilnehmer, für den der Medikationsplan dokumentiert wird.</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -652,7 +652,7 @@
 </t>
   </si>
   <si>
-    <t>Datum der letzten Aktualisierung der Liste.</t>
+    <t>Letzte Aktualisierung des Medikationsplans.</t>
   </si>
   <si>
     <t>The date that the list was prepared.</t>
@@ -681,9 +681,9 @@
 </t>
   </si>
   <si>
-    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. 
-Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
-des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den ZPI.</t>
+    <t>Ersteller des Medikationsplans und für den Inhalt verantwortlich. 
+Im Falle eines GDA: Eindeutig identifiziert über den GDA-Index und berechtigt auf die e-Medikation 
+des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. ELGA-Teilnehmer nur Ausübung seiner Teilnehmerrechte (Löschen von Einträgen).</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -732,7 +732,7 @@
 </t>
   </si>
   <si>
-    <t>Keine Freitext-Anmerkungen auf Listenebene.</t>
+    <t>Keine Freitext-Anmerkungen im Medikationsplan.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -748,7 +748,7 @@
 </t>
   </si>
   <si>
-    <t>Die Reihenfolge der Listeneinträge ist fachlich relevant und wird durch den Ersteller durch die Reihung der Eintries festgelegt.</t>
+    <t>Medikationsplaneinträge. Die Reihenfolge der Medikationsplaneinträge ist fachlich relevant und wird durch den Ersteller durch die Reihung der Eintries festgelegt.</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -808,7 +808,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Listeneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Eintrag wird hinzugefügt | Unchanged: Bestehender Eintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Eintrag wird geändert | Removed: Bestehender Eintrag wird entfernt</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Planeintrag wird hinzugefügt | Unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Planeintrag wird geändert | Removed: Bestehender Planeintrag wird entfernt</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -820,7 +820,7 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEntryFlagVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEntryFlagVS</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -830,7 +830,7 @@
 </t>
   </si>
   <si>
-    <t>Keine Verwendung in der ELGA Core List (da list.mode immer working).</t>
+    <t>Keine Verwendung im Medikationsplan (da list.mode immer working).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -855,7 +855,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Kein Datum der Aufnahme bzw. Änderung des Eintrags im List.entry. Das Datum ist nur im in der referenzierten Ressource ersichtlich.</t>
+    <t>Kein Datum der Aufnahme bzw. Änderung des Eintrags im Medikationsplan. Das Datum ist nur im referenzierten Medikationsplaneintrag ersichtlich.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -886,7 +886,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum die Liste leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Die Liste wurde explizit geleert.</t>
+    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -898,7 +898,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEmptyReasonVS</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1254,7 +1254,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="36.34375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>85</v>
